--- a/lecture_pptx/session15_assets/引受判定マスタ_テンプレ.xlsx
+++ b/lecture_pptx/session15_assets/引受判定マスタ_テンプレ.xlsx
@@ -67,7 +67,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +116,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
@@ -126,7 +131,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECEFF1"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -238,6 +263,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,11 +274,23 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -629,22 +669,22 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="78" customHeight="1">
+    <row r="1" ht="88" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>■ 引受判定マスタ表 (10列) ─ 1行 = 1つの判定ルール
-デモナレッジ 01〜06 から条件を抽出し、この表に 1行ずつ書き込む。
-完成イメージが分からない時は 別シート「引受判定マスタ_記入例」を参照(そのままコピー禁止)。
-同じ条件が複数のナレッジに出てきた時は 1行に統合、根拠列に両方書く。</t>
+          <t>■ 引受判定マスタ表 (10列) ─ 1行 = 1 (条件 × 保険会社 × 商品ジャンル) の判定
+デモナレッジ 01〜06 から 「この条件は どの会社の どの商品では 何になる?」を抽出し、この表に 1行ずつ書き込む。
+同じ条件でも会社で判定が違う場合は 別の行 に書く(会社ごとに横並びで比較できる形にする)。
+完成イメージが分からない時は 別シート「引受判定マスタ_記入例」を参照(そのままコピー禁止)。</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -670,37 +710,37 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>C: 対象商品</t>
+          <t>C: 保険会社</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>D: 条件詳細</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>E: 判定</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>F: 判定理由</t>
+          <t>D: 商品ジャンル</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>E: 条件詳細</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>F: 判定</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>G: 追加確認 or 代替案</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>H: エスカレ先</t>
+          <t>G: 判定理由</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>H: 対応(追加確認 / NG時の代替候補社)</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>I: 根拠</t>
+          <t>I: 情報源</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
@@ -717,42 +757,42 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>年齢</t>
+          <t>健康</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>(ここに条件を書く 例:20歳未満)</t>
-        </is>
-      </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>(条件を書く 例:高血圧180超)</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>(なぜこの判定?を1文で)</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>(追加確認項目 or 代替案)</t>
+          <t>(なぜ)</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>(部署/担当)</t>
+          <t>代替: (どの会社なら通りそうか)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>(内規§/文書名 or "口伝")</t>
+          <t>(A社研修 §/営業担当メール/先輩口伝)</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
@@ -847,22 +887,23 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="72" customHeight="1">
+    <row r="1" ht="88" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>■ この見本の使い方
-デモナレッジ 01〜06 を整理して マスタ表に統合したら、こうなる、という完成見本(25行)。
-骨格の参考として眺めてから、「引受判定マスタ」シートに戻って 自社の実情に合わせて書き直してください。
-⚠️ そのままコピペせず、自分の営業対象・自社商品に合わせて再解釈すること。</t>
+デモナレッジ 01〜06 を整理して 代理店マスタ表に統合したら こうなる、という完成見本(25行)。
+「同じ条件でも会社で判定が違う」ケースを あえて隣り合わせて配置してある(例: 高血圧180超で A社NG / B社要確認)。
+骨格の参考として眺めてから、「引受判定マスタ」シートに戻って 自分が扱っている会社・商品に合わせて書き直してください。
+⚠️ そのままコピペせず、自分の代理店契約している保険会社の実データで再構築すること。</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -888,37 +929,37 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>C: 対象商品</t>
+          <t>C: 保険会社</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>D: 条件詳細</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>E: 判定</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>F: 判定理由</t>
+          <t>D: 商品ジャンル</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>E: 条件詳細</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>F: 判定</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>G: 追加確認 or 代替案</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>H: エスカレ先</t>
+          <t>G: 判定理由</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>H: 対応(追加確認 / NG時の代替候補社)</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>I: 根拠</t>
+          <t>I: 情報源</t>
         </is>
       </c>
       <c r="J2" s="9" t="inlineStr">
@@ -935,42 +976,42 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>年齢</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>加入希望者が20歳未満</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>高血圧 コントロール良好(160未満、1年以上安定)</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>未成年でも法定代理人同意があれば加入可能</t>
-        </is>
-      </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>追加確認: 法定代理人同意書</t>
+          <t>血圧安定なら通常引受</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>引受査定課</t>
+          <t>追加確認: 主治医の"コントロール良好"診断書</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>保険業法§309 / 田中課長 QAメール(2024/08)</t>
+          <t>A社営業(田中さん)チャット 2024/03</t>
         </is>
       </c>
       <c r="J3" s="12" t="inlineStr">
@@ -980,54 +1021,54 @@
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>RULE-002</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>年齢</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>加入希望者が18歳未満</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>高血圧 160超〜180未満</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>未成年の死亡保障は道徳上慎重に判定</t>
-        </is>
-      </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 保護者同意書+加入目的の詳細ヒアリング</t>
+          <t>160超で査定に回る</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>引受査定課(モラル担当)</t>
+          <t>追加確認: 直近3ヶ月血圧記録+診断書</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>内規§2.1 / 田中課長 QAメール(2024/08)</t>
+          <t>A社研修資料 v2024 §3.2</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14 佐藤</t>
+          <t>2026-07-14 田中</t>
         </is>
       </c>
     </row>
@@ -1039,94 +1080,94 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>年齢</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>加入希望者が70歳以上</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>高血圧 180超</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>180超は A社で引受不可</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>代替: B社医療で要確認扱いなら通る可能性</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>A社研修資料 v2024 §3.2 / A社営業チャット 2024/06</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-14 田中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>RULE-004</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>B社生命</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>高血圧 180超</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>高年齢は疾病リスク上昇、健康告知の厳密確認要</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>追加確認: 直近1年の健康診断結果</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>引受査定課 Aチーム</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>商品パンフ 2024年版 p.5 / Slackログ(2024/10/14)</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-14 田中</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>RULE-004</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>健康</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>医療</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>高血圧治療中で 収縮期160mmHg以上</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>血圧コントロール状態により条件付き引受の可能性</t>
-        </is>
-      </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 診断書+直近3ヶ月血圧記録</t>
+          <t>B社は個別査定で通る可能性</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 Aチーム</t>
+          <t>追加確認: 診断書+血圧測定記録+主治医コメント</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §3.2 / 商品パンフ 2024年版</t>
+          <t>B社営業(佐藤さん)チャット 2024/06 / 先輩口伝</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -1146,96 +1187,96 @@
           <t>健康</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>高血圧治療中でコントロール良好(1年以上)</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>コントロール良好で服薬安定なら引受可</t>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>妊娠中(妊娠12週未満)</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>追加確認: 主治医の"コントロール良好"診断書</t>
+          <t>A社は12週未満は引受不可</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代替: B社医療なら妊娠告知項目なしで加入可</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>田中課長 口伝メモ(要正式化)</t>
+          <t>先輩代理店口伝 / QAメール(2024/04)</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-14 田中</t>
+          <t>2026-07-14 佐藤</t>
         </is>
       </c>
     </row>
     <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>RULE-006</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>既往歴</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>直近1年以内に入院歴あり</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>再発リスクが高く医療保険引受不可</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>妊娠中(妊娠12週以降で安定)</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>代替案: 引受基準緩和型医療保険を案内</t>
+          <t>12週以降でも安定確認要</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: 母子手帳の写し</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §4.1 / 商品パンフ 2024年版</t>
+          <t>QAメール(2024/04) 山田さん</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14 田中</t>
+          <t>2026-07-14 佐藤</t>
         </is>
       </c>
     </row>
@@ -1247,94 +1288,94 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>B社生命</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>妊娠中(週数問わず)</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>B社は妊娠の告知項目そのものが無い</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>母子手帳の写し等の追加提出は不要</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>B社営業(佐藤さん)チャット 2024/07 / B社パンフ</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-14 佐藤</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>RULE-008</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
           <t>既往歴</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>5年以上前に入院歴、完治済み</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>5年経過で寛解と判断</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>追加確認: 完治証明の診断書</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>医療保険引受基準書 v2019 §4.2 / 田中課長 口伝メモ</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-14 田中</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>RULE-008</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>既往歴</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>がん</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>がん既往歴あり(治療完了後3年未満)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>糖尿病1型</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>再発リスクにより引受不可</t>
-        </is>
-      </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>代替案: 引受基準緩和型/無告知型商品</t>
+          <t>A社は1型は原則NG</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代替: B社医療で要確認扱いで打診 / D社ライトが最終候補</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Slackログ(2024/05/07)/ 商品パンフ Gold</t>
+          <t>先輩代理店口伝 / A社研修 §3.4</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -1354,91 +1395,91 @@
           <t>既往歴</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>がん</t>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>B社生命</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>がん既往歴あり(治療完了後5年経過、再発なし)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>糖尿病1型(コントロール良好)</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>5年寛解基準に近いが個別確認要</t>
-        </is>
-      </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>追加確認: 主治医の寛解証明+直近1年検査結果</t>
+          <t>B社は個別査定で通る可能性</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>引受査定課 がんチーム</t>
+          <t>追加確認: HbA1c直近3ヶ月+合併症の有無</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Slackログ(2024/05/07)</t>
+          <t>B社営業(佐藤さん)チャット 2024/05 / 先輩口伝</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-14 佐藤</t>
+          <t>2026-07-14 田中</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>RULE-010</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>職業</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>D社生命</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>建設業 高所作業(20m以上)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>職業リスク上昇、保険金額により条件変動</t>
+          <t>医療(緩和型)</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>糖尿病1型でも 3項目告知で該当なし</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 職務内容の詳細+作業頻度</t>
+          <t>緩和型なので個別疾患ではなく告知3項目で判定</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 職業リスク担当</t>
+          <t>過去1年入院/5年手術/がん治療の3項目に該当が無ければ加入可</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §5.3 / 雑エクセル(山田作)</t>
+          <t>D社商品パンフ ライト</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -1455,42 +1496,42 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>職業</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>消防士(現役)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>YES(条件付)</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>職業リスクは加算されるが引受可能</t>
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>糖尿病2型(HbA1c 7.0未満、コントロール良好)</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>保険料10%加算</t>
+          <t>コントロール良好で引受可</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: HbA1c直近1年記録</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>商品パンフ 2024年版 p.12 / 雑エクセル(山田作)</t>
+          <t>A社研修資料 v2024 §3.4</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1500,54 +1541,54 @@
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>RULE-012</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>金額</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>死亡保険金額 3億円超</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>高額保険金は年収バランスと目的確認要</t>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>がん既往(治療完了3年経過、再発なし)</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 年収証明+加入目的書</t>
+          <t>A社は5年経過必須</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 高額担当</t>
+          <t>代替: B社がん(要確認)/ C社は5年経過待ち / 緩和型D社</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>商品パンフ プレミアム / 雑エクセル(山田作)</t>
+          <t>A社研修資料 v2024 §6.1</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14 佐藤</t>
+          <t>2026-07-14 田中</t>
         </is>
       </c>
     </row>
@@ -1559,99 +1600,99 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>金額</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>B社生命</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>がん</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>がん保険金 3000万円超</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>がん保険は個別に金額上限あり</t>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>がん既往(治療完了3年経過、再発なし)</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>代替案: 上限内での加入検討</t>
+          <t>B社は3年で個別査定に回してくれる</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: 主治医の寛解証明+直近1年検査結果</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Slackログ(2024/06/22) / 商品パンフ Gold</t>
+          <t>B社営業(佐藤さん)メール 2024/04</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
+          <t>2026-07-14 佐藤</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>RULE-014</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>C社生命</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>がん既往(治療完了5年経過、再発なし)</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>C社は5年寛解で通常引受</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="inlineStr">
+        <is>
+          <t>追加確認: 寛解証明</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>C社商品パンフ Gold / C社営業チャット 2024/09</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
           <t>2026-07-14 田中</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>RULE-014</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>健康</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>全て</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>妊娠中(妊娠12週未満)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>経過初期は医的告知が不安定</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>追加確認: 現在の妊娠週数+医師のOK</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>引受査定課</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Slackログ(2024/09/08)/ QAメール(2024/04)</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>2026-07-14 佐藤</t>
         </is>
       </c>
     </row>
@@ -1663,94 +1704,94 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>健康</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>医療</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>妊娠中(妊娠12週以降で安定)</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>直近1年以内に入院歴あり</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>A社は1年以内入院NG</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>代替: D社ライト(緩和型)を打診</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>A社研修資料 v2024 §4.1</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-14 田中</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>RULE-016</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>既往歴</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>5年以上前の入院歴、完治済み</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>安定期の医療保険は引受可能</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>追加確認: 母子手帳の写し</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>QAメール(2024/04) 田中課長</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-14 佐藤</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>RULE-016</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>全て</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>手術予定が3ヶ月以内</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>手術直前は引受不可(モラルリスク)</t>
-        </is>
-      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>代替案: 手術完了後6ヶ月経過してからの申込を提案</t>
+          <t>5年経過で寛解と判断</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: 完治証明</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Slackログ(2024/03/12) / 雑エクセル(山田作)</t>
+          <t>A社研修資料 v2024 §4.2</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
@@ -1767,42 +1808,42 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>医療</t>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>歯科手術予定</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>歯科は原則対象外なので通常引受</t>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>建設業 高所作業(20m以上)</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>職業リスクで査定要</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: 職務内容+作業頻度</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Slackログ(2024/03/12) 田中課長・例外扱い</t>
+          <t>A社商品パンフ プレミアム</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -1812,49 +1853,49 @@
       </c>
     </row>
     <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>RULE-018</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>既往歴</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>医療</t>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>糖尿病1型(45歳以上)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>従来NG だがコントロール良好なら要確認扱い</t>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>消防士(現役)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>YES(条件付)</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>追加確認: HbA1c直近3ヶ月+合併症の有無</t>
+          <t>職業リスクで保険料調整</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 内分泌担当</t>
+          <t>保険料10%加算で引受</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>ベテラン口伝メモ(要正式化)</t>
+          <t>A社商品パンフ プレミアム / 過去申込 井上様(2024/12)</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -1871,42 +1912,42 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>既往歴</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>医療</t>
+          <t>職業</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>糖尿病2型(コントロール良好)</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>コントロール良好で合併症なしなら引受可</t>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>スタントマン等 危険職業</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>追加確認: HbA1c 7.0未満の直近1年記録</t>
+          <t>危険職業は引受不可</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代替: D社ライト(緩和型)</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §3.4</t>
+          <t>A社研修資料 v2024 §5.4 / 過去申込 森様(2025/01)</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -1916,54 +1957,54 @@
       </c>
     </row>
     <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>RULE-020</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>職業</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>死亡</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>危険職業(スタント/レーサー等)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>職業リスクが基準を超えるため</t>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>死亡保険金 3億円超</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>代替案: 引受基準緩和型商品</t>
+          <t>高額査定チームへ</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>追加確認: 年収証明+加入目的書</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §5.4 / 雑エクセル(山田作)</t>
+          <t>A社商品パンフ プレミアム / 過去申込 木村様(2024/11)</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14 田中</t>
+          <t>2026-07-14 佐藤</t>
         </is>
       </c>
     </row>
@@ -1975,99 +2016,99 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>C社生命</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>がん</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>がん保険金 3000万円超</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>C社Goldは3000万円上限</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>代替: B社がんベーシック(上限5000万まで可)</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>C社商品パンフ Gold / 過去申込 長谷川様(2024/11)</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-14 田中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="72" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>RULE-022</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>学資</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>契約者が65歳以上</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>加入希望者 70歳以上</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>学資は契約者の払込能力確認要</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>追加確認: 収入証明+払込期間の設計</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>引受査定課</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>QAメール(2024/06) / 商品パンフ 学資</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-14 佐藤</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="72" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>RULE-022</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>健康</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>医療</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>精神疾患通院歴(5年以内)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>病状と治療期間により個別判定</t>
-        </is>
-      </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 主治医診断書+服薬状況</t>
+          <t>高年齢は健康告知の厳密確認要</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 メンタル担当</t>
+          <t>追加確認: 直近1年健康診断結果</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>医療保険引受基準書 v2019 §3.6</t>
+          <t>A社商品パンフ プレミアム p.5</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>2026-07-14 佐藤</t>
+          <t>2026-07-14 田中</t>
         </is>
       </c>
     </row>
@@ -2079,42 +2120,42 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>職業</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>死亡</t>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>B社生命</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>職業なし・専業主婦(主夫)</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>職業リスクは低く通常引受</t>
+          <t>医療</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>加入希望者 75歳以上</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>B社医療は75歳未満まで</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>代替: F社シルバー医療(70〜85歳対応)</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>商品パンフ プレミアム(既定通り)</t>
+          <t>B社商品パンフ / F社商品パンフ / 過去申込 中村様(2024/10)</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -2124,49 +2165,49 @@
       </c>
     </row>
     <row r="26" ht="72" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>RULE-024</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>全て</t>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>A社生命</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>犯罪歴あり(執行猶予中含む)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
+          <t>学資</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>契約者が65歳以上</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>モラルリスクの個別判定要</t>
-        </is>
-      </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>追加確認: 詳細ヒアリング</t>
+          <t>契約者の払込能力確認要</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>引受査定課 モラル担当</t>
+          <t>追加確認: 収入証明+払込期間の設計 / 代替: C社に事前相談</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>田中課長 口伝メモ(要正式化)</t>
+          <t>A社商品パンフ 学資 / QAメール(2024/06)</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -2186,39 +2227,39 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>全て</t>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>全社共通</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>海外居住(帰国後1年未満)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>海外での治療歴の確認要</t>
+          <t>死亡・医療</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>手術予定 3ヶ月以内</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>追加確認: 海外医療機関記録+入国後健康診断</t>
+          <t>全社モラルリスクで引受不可(歯科手術は除く)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>引受査定課</t>
+          <t>代替: 手術完了後6ヶ月経過してから再申込を提案</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>田中課長 口伝メモ(要正式化)</t>
+          <t>先輩代理店口伝 / A社営業チャット 2024/09</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
@@ -2251,11 +2292,12 @@
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>■ 更新ログ ─ マスタ表の変更履歴を残すシート
-「削除」ではなく「無効化」で運用(履歴が消えないように)。月1回15分の見直し会議のたびに記入。</t>
+「削除」ではなく「無効化」で運用(履歴が消えないように)。月1回15分の見直し会議のたびに記入。
+各社の改定情報を掴んだら、まずここに書き込んでからマスタ表を更新。</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2291,81 +2333,81 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>RULE-018</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>RULE-007</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>追加</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>糖尿病1型(45歳以上)を要確認扱いに追加。田中課長口伝を正式ルール化</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>B社が妊娠告知項目を廃止した情報を反映(2024/07 B社佐藤さんチャット)</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>佐藤</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>RULE-023</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>追加</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>F社シルバー医療(70-85歳)を代替候補として追加。中村様案件で有効性確認</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>RULE-005</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>RULE-012</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>「1年以上コントロール良好」の基準を明確化(以前は "しばらく安定")</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>佐藤</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>RULE-025</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>追加</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>海外居住(帰国後1年未満)を要確認扱いに追加</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>A社がん5年経過必須の情報を A社研修資料 v2024 §6.1 で正式化</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>田中</t>
         </is>
